--- a/artfynd/A 30364-2022 artfynd.xlsx
+++ b/artfynd/A 30364-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124558024</v>
+        <v>124558003</v>
       </c>
       <c r="B2" t="n">
-        <v>79795</v>
+        <v>100279</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -765,21 +770,6 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -796,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124558003</v>
+        <v>124558024</v>
       </c>
       <c r="B3" t="n">
-        <v>100279</v>
+        <v>79795</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,31 +802,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -891,6 +876,21 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">

--- a/artfynd/A 30364-2022 artfynd.xlsx
+++ b/artfynd/A 30364-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124558003</v>
+        <v>124558024</v>
       </c>
       <c r="B2" t="n">
-        <v>100279</v>
+        <v>79795</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -770,6 +765,21 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -786,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124558024</v>
+        <v>124558003</v>
       </c>
       <c r="B3" t="n">
-        <v>79795</v>
+        <v>100279</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,26 +812,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -876,21 +891,6 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
